--- a/inputs/styles_cross_nrg.xlsx
+++ b/inputs/styles_cross_nrg.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" r:id="Rb0b1d19aed7145ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Beer Review" sheetId="2" r:id="Re9ec42948bfd4fd9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Family Summary" sheetId="3" r:id="Re96c833b630d4027"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method &amp; Sources" sheetId="4" r:id="Rb615e7efe2334262"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" r:id="Rca3eafad67f44905"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Beer Review" sheetId="2" r:id="R90804f0b31ef4ee0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Family Summary" sheetId="3" r:id="Re1c39a1854c1419b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method &amp; Sources" sheetId="4" r:id="R756dc7e6425e46d7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -627,7 +627,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NRGStyleCrosswalk" displayName="NRGStyleCrosswalk" ref="A1:G114" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NRGStyleCrosswalk" displayName="NRGStyleCrosswalk" ref="A1:G115" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="Style"/>
     <x:tableColumn id="2" name="Style Family"/>
@@ -902,7 +902,7 @@
       <x:c r="E2" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F2" s="6" t="str"/>
+      <x:c r="F2" s="6"/>
       <x:c r="G2" s="7" t="str">
         <x:v>Fermentation- or ingredient-led fruit/spice without sourness as the defining trait.</x:v>
       </x:c>
@@ -923,7 +923,7 @@
       <x:c r="E3" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F3" s="6" t="str"/>
+      <x:c r="F3" s="6"/>
       <x:c r="G3" s="7" t="str">
         <x:v>Fermentation- or ingredient-led fruit/spice without sourness as the defining trait.</x:v>
       </x:c>
@@ -944,7 +944,7 @@
       <x:c r="E4" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F4" s="6" t="str"/>
+      <x:c r="F4" s="6"/>
       <x:c r="G4" s="7" t="str">
         <x:v>Fermentation- or ingredient-led fruit/spice without sourness as the defining trait.</x:v>
       </x:c>
@@ -965,7 +965,7 @@
       <x:c r="E5" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F5" s="6" t="str"/>
+      <x:c r="F5" s="6"/>
       <x:c r="G5" s="7" t="str">
         <x:v>Fermentation- or ingredient-led fruit/spice without sourness as the defining trait.</x:v>
       </x:c>
@@ -986,7 +986,7 @@
       <x:c r="E6" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F6" s="6" t="str"/>
+      <x:c r="F6" s="6"/>
       <x:c r="G6" s="7" t="str">
         <x:v>Toasty, nutty, caramel, or toffee-led profile; NRG's Malt family.</x:v>
       </x:c>
@@ -1007,7 +1007,7 @@
       <x:c r="E7" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F7" s="6" t="str"/>
+      <x:c r="F7" s="6"/>
       <x:c r="G7" s="7" t="str">
         <x:v>Clean, refreshing lager/blond/wheat profile; NRG's Crisp family.</x:v>
       </x:c>
@@ -1028,7 +1028,7 @@
       <x:c r="E8" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F8" s="6" t="str"/>
+      <x:c r="F8" s="6"/>
       <x:c r="G8" s="7" t="str">
         <x:v>Clean, refreshing lager/blond/wheat profile; NRG's Crisp family.</x:v>
       </x:c>
@@ -1049,7 +1049,7 @@
       <x:c r="E9" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F9" s="6" t="str"/>
+      <x:c r="F9" s="6"/>
       <x:c r="G9" s="7" t="str">
         <x:v>Toasty, nutty, caramel, or toffee-led profile; NRG's Malt family.</x:v>
       </x:c>
@@ -1070,7 +1070,7 @@
       <x:c r="E10" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F10" s="6" t="str"/>
+      <x:c r="F10" s="6"/>
       <x:c r="G10" s="7" t="str">
         <x:v>Clean, refreshing lager/blond/wheat profile; NRG's Crisp family.</x:v>
       </x:c>
@@ -1091,7 +1091,7 @@
       <x:c r="E11" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F11" s="6" t="str"/>
+      <x:c r="F11" s="6"/>
       <x:c r="G11" s="7" t="str">
         <x:v>Toasty, nutty, caramel, or toffee-led profile; NRG's Malt family.</x:v>
       </x:c>
@@ -1112,7 +1112,7 @@
       <x:c r="E12" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F12" s="6" t="str"/>
+      <x:c r="F12" s="6"/>
       <x:c r="G12" s="7" t="str">
         <x:v>Fermentation- or ingredient-led fruit/spice without sourness as the defining trait.</x:v>
       </x:c>
@@ -1133,7 +1133,7 @@
       <x:c r="E13" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F13" s="6" t="str"/>
+      <x:c r="F13" s="6"/>
       <x:c r="G13" s="7" t="str">
         <x:v>Acidity, Brett, mixed/spontaneous fermentation, or lambic character defines the style.</x:v>
       </x:c>
@@ -1154,7 +1154,7 @@
       <x:c r="E14" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F14" s="6" t="str"/>
+      <x:c r="F14" s="6"/>
       <x:c r="G14" s="7" t="str">
         <x:v>Dark malt, cocoa, coffee, or char-led profile; NRG's Roast family.</x:v>
       </x:c>
@@ -1175,7 +1175,7 @@
       <x:c r="E15" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F15" s="6" t="str"/>
+      <x:c r="F15" s="6"/>
       <x:c r="G15" s="7" t="str">
         <x:v>Hop aroma or bitterness is the defining flavor; NRG's Hop family.</x:v>
       </x:c>
@@ -1219,7 +1219,7 @@
       <x:c r="E17" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F17" s="6" t="str"/>
+      <x:c r="F17" s="6"/>
       <x:c r="G17" s="7" t="str">
         <x:v>Acidity, Brett, mixed/spontaneous fermentation, or lambic character defines the style.</x:v>
       </x:c>
@@ -1309,7 +1309,7 @@
       <x:c r="E21" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F21" s="6" t="str"/>
+      <x:c r="F21" s="6"/>
       <x:c r="G21" s="7" t="str">
         <x:v>Clean, refreshing lager/blond/wheat profile; NRG's Crisp family.</x:v>
       </x:c>
@@ -1399,7 +1399,7 @@
       <x:c r="E25" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F25" s="6" t="str"/>
+      <x:c r="F25" s="6"/>
       <x:c r="G25" s="7" t="str">
         <x:v>Smoked malt is style-defining; NRG's Smoke family.</x:v>
       </x:c>
@@ -1420,7 +1420,7 @@
       <x:c r="E26" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F26" s="6" t="str"/>
+      <x:c r="F26" s="6"/>
       <x:c r="G26" s="7" t="str">
         <x:v>All Lichtenhainer maps to Smoke. BJCP defines it as a smoked sour beer and describes its smoke aroma as moderately strong.</x:v>
       </x:c>
@@ -1441,7 +1441,7 @@
       <x:c r="E27" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F27" s="6" t="str"/>
+      <x:c r="F27" s="6"/>
       <x:c r="G27" s="7" t="str">
         <x:v>Clean, refreshing lager/blond/wheat profile; NRG's Crisp family.</x:v>
       </x:c>
@@ -1462,7 +1462,7 @@
       <x:c r="E28" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F28" s="6" t="str"/>
+      <x:c r="F28" s="6"/>
       <x:c r="G28" s="7" t="str">
         <x:v>Fermentation- or ingredient-led fruit/spice without sourness as the defining trait.</x:v>
       </x:c>
@@ -1475,7 +1475,7 @@
         <x:v>Hop</x:v>
       </x:c>
       <x:c r="C29" s="5" t="n">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D29" s="6" t="str">
         <x:v>Yes</x:v>
@@ -1483,7 +1483,7 @@
       <x:c r="E29" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F29" s="6" t="str"/>
+      <x:c r="F29" s="6"/>
       <x:c r="G29" s="7" t="str">
         <x:v>Hop aroma or bitterness is the defining flavor; NRG's Hop family.</x:v>
       </x:c>
@@ -1504,7 +1504,7 @@
       <x:c r="E30" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F30" s="6" t="str"/>
+      <x:c r="F30" s="6"/>
       <x:c r="G30" s="7" t="str">
         <x:v>Dark malt, cocoa, coffee, or char-led profile; NRG's Roast family.</x:v>
       </x:c>
@@ -1525,7 +1525,7 @@
       <x:c r="E31" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F31" s="6" t="str"/>
+      <x:c r="F31" s="6"/>
       <x:c r="G31" s="7" t="str">
         <x:v>Hop aroma or bitterness is the defining flavor; NRG's Hop family.</x:v>
       </x:c>
@@ -1538,7 +1538,7 @@
         <x:v>Hop</x:v>
       </x:c>
       <x:c r="C32" s="5" t="n">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D32" s="6" t="str">
         <x:v>Yes</x:v>
@@ -1546,7 +1546,7 @@
       <x:c r="E32" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F32" s="6" t="str"/>
+      <x:c r="F32" s="6"/>
       <x:c r="G32" s="7" t="str">
         <x:v>Hop aroma or bitterness is the defining flavor; NRG's Hop family.</x:v>
       </x:c>
@@ -1567,7 +1567,7 @@
       <x:c r="E33" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F33" s="6" t="str"/>
+      <x:c r="F33" s="6"/>
       <x:c r="G33" s="7" t="str">
         <x:v>Dark malt, cocoa, coffee, or char-led profile; NRG's Roast family.</x:v>
       </x:c>
@@ -1588,7 +1588,7 @@
       <x:c r="E34" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F34" s="6" t="str"/>
+      <x:c r="F34" s="6"/>
       <x:c r="G34" s="7" t="str">
         <x:v>Hop aroma or bitterness is the defining flavor; NRG's Hop family.</x:v>
       </x:c>
@@ -1609,7 +1609,7 @@
       <x:c r="E35" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F35" s="6" t="str"/>
+      <x:c r="F35" s="6"/>
       <x:c r="G35" s="7" t="str">
         <x:v>Hop aroma or bitterness is the defining flavor; NRG's Hop family.</x:v>
       </x:c>
@@ -1630,7 +1630,7 @@
       <x:c r="E36" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F36" s="6" t="str"/>
+      <x:c r="F36" s="6"/>
       <x:c r="G36" s="7" t="str">
         <x:v>Hop aroma or bitterness is the defining flavor; NRG's Hop family.</x:v>
       </x:c>
@@ -1643,7 +1643,7 @@
         <x:v>Hop</x:v>
       </x:c>
       <x:c r="C37" s="5" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D37" s="6" t="str">
         <x:v>Yes</x:v>
@@ -1651,7 +1651,7 @@
       <x:c r="E37" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F37" s="6" t="str"/>
+      <x:c r="F37" s="6"/>
       <x:c r="G37" s="7" t="str">
         <x:v>Hop aroma or bitterness is the defining flavor; NRG's Hop family.</x:v>
       </x:c>
@@ -1672,7 +1672,7 @@
       <x:c r="E38" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F38" s="6" t="str"/>
+      <x:c r="F38" s="6"/>
       <x:c r="G38" s="7" t="str">
         <x:v>Hop aroma or bitterness is the defining flavor; NRG's Hop family.</x:v>
       </x:c>
@@ -1693,7 +1693,7 @@
       <x:c r="E39" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F39" s="6" t="str"/>
+      <x:c r="F39" s="6"/>
       <x:c r="G39" s="7" t="str">
         <x:v>Hop aroma or bitterness is the defining flavor; NRG's Hop family.</x:v>
       </x:c>
@@ -1714,7 +1714,7 @@
       <x:c r="E40" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F40" s="6" t="str"/>
+      <x:c r="F40" s="6"/>
       <x:c r="G40" s="7" t="str">
         <x:v>Hop aroma or bitterness is the defining flavor; NRG's Hop family.</x:v>
       </x:c>
@@ -1735,7 +1735,7 @@
       <x:c r="E41" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F41" s="6" t="str"/>
+      <x:c r="F41" s="6"/>
       <x:c r="G41" s="7" t="str">
         <x:v>Hop aroma or bitterness is the defining flavor; NRG's Hop family.</x:v>
       </x:c>
@@ -1756,7 +1756,7 @@
       <x:c r="E42" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F42" s="6" t="str"/>
+      <x:c r="F42" s="6"/>
       <x:c r="G42" s="7" t="str">
         <x:v>Acidity, Brett, mixed/spontaneous fermentation, or lambic character defines the style.</x:v>
       </x:c>
@@ -1777,7 +1777,7 @@
       <x:c r="E43" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F43" s="6" t="str"/>
+      <x:c r="F43" s="6"/>
       <x:c r="G43" s="7" t="str">
         <x:v>Hop aroma or bitterness is the defining flavor; NRG's Hop family.</x:v>
       </x:c>
@@ -1798,7 +1798,7 @@
       <x:c r="E44" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F44" s="6" t="str"/>
+      <x:c r="F44" s="6"/>
       <x:c r="G44" s="7" t="str">
         <x:v>Clean, refreshing lager/blond/wheat profile; NRG's Crisp family.</x:v>
       </x:c>
@@ -1819,7 +1819,7 @@
       <x:c r="E45" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F45" s="6" t="str"/>
+      <x:c r="F45" s="6"/>
       <x:c r="G45" s="7" t="str">
         <x:v>Clean, refreshing lager/blond/wheat profile; NRG's Crisp family.</x:v>
       </x:c>
@@ -1840,7 +1840,7 @@
       <x:c r="E46" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F46" s="6" t="str"/>
+      <x:c r="F46" s="6"/>
       <x:c r="G46" s="7" t="str">
         <x:v>Clean, refreshing lager/blond/wheat profile; NRG's Crisp family.</x:v>
       </x:c>
@@ -1861,7 +1861,7 @@
       <x:c r="E47" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F47" s="6" t="str"/>
+      <x:c r="F47" s="6"/>
       <x:c r="G47" s="7" t="str">
         <x:v>Clean, refreshing lager/blond/wheat profile; NRG's Crisp family.</x:v>
       </x:c>
@@ -1882,7 +1882,7 @@
       <x:c r="E48" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F48" s="6" t="str"/>
+      <x:c r="F48" s="6"/>
       <x:c r="G48" s="7" t="str">
         <x:v>Clean, refreshing lager/blond/wheat profile; NRG's Crisp family.</x:v>
       </x:c>
@@ -1903,7 +1903,7 @@
       <x:c r="E49" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F49" s="6" t="str"/>
+      <x:c r="F49" s="6"/>
       <x:c r="G49" s="7" t="str">
         <x:v>Clean, refreshing lager/blond/wheat profile; NRG's Crisp family.</x:v>
       </x:c>
@@ -1924,7 +1924,7 @@
       <x:c r="E50" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F50" s="6" t="str"/>
+      <x:c r="F50" s="6"/>
       <x:c r="G50" s="7" t="str">
         <x:v>Clean, refreshing lager/blond/wheat profile; NRG's Crisp family.</x:v>
       </x:c>
@@ -1968,7 +1968,7 @@
       <x:c r="E52" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F52" s="6" t="str"/>
+      <x:c r="F52" s="6"/>
       <x:c r="G52" s="7" t="str">
         <x:v>Clean, refreshing lager/blond/wheat profile; NRG's Crisp family.</x:v>
       </x:c>
@@ -1981,7 +1981,7 @@
         <x:v>Crisp</x:v>
       </x:c>
       <x:c r="C53" s="5" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D53" s="6" t="str">
         <x:v>Yes</x:v>
@@ -1989,7 +1989,7 @@
       <x:c r="E53" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F53" s="6" t="str"/>
+      <x:c r="F53" s="6"/>
       <x:c r="G53" s="7" t="str">
         <x:v>Clean, refreshing lager/blond/wheat profile; NRG's Crisp family.</x:v>
       </x:c>
@@ -2010,7 +2010,7 @@
       <x:c r="E54" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F54" s="6" t="str"/>
+      <x:c r="F54" s="6"/>
       <x:c r="G54" s="7" t="str">
         <x:v>Toasty, nutty, caramel, or toffee-led profile; NRG's Malt family.</x:v>
       </x:c>
@@ -2054,7 +2054,7 @@
       <x:c r="E56" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F56" s="6" t="str"/>
+      <x:c r="F56" s="6"/>
       <x:c r="G56" s="7" t="str">
         <x:v>Clean, refreshing lager/blond/wheat profile; NRG's Crisp family.</x:v>
       </x:c>
@@ -2075,7 +2075,7 @@
       <x:c r="E57" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F57" s="6" t="str"/>
+      <x:c r="F57" s="6"/>
       <x:c r="G57" s="7" t="str">
         <x:v>Clean, refreshing lager/blond/wheat profile; NRG's Crisp family.</x:v>
       </x:c>
@@ -2096,7 +2096,7 @@
       <x:c r="E58" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F58" s="6" t="str"/>
+      <x:c r="F58" s="6"/>
       <x:c r="G58" s="7" t="str">
         <x:v>Smoked malt is style-defining; NRG's Smoke family.</x:v>
       </x:c>
@@ -2132,7 +2132,7 @@
         <x:v>Crisp</x:v>
       </x:c>
       <x:c r="C60" s="5" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D60" s="6" t="str">
         <x:v>Yes</x:v>
@@ -2140,7 +2140,7 @@
       <x:c r="E60" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F60" s="6" t="str"/>
+      <x:c r="F60" s="6"/>
       <x:c r="G60" s="7" t="str">
         <x:v>Clean, refreshing lager/blond/wheat profile; NRG's Crisp family.</x:v>
       </x:c>
@@ -2161,7 +2161,7 @@
       <x:c r="E61" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F61" s="6" t="str"/>
+      <x:c r="F61" s="6"/>
       <x:c r="G61" s="7" t="str">
         <x:v>All Czech dark lagers map to Malt. BJCP says deep, complex maltiness dominates; roast varies and should not overwhelm the base malt.</x:v>
       </x:c>
@@ -2182,7 +2182,7 @@
       <x:c r="E62" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F62" s="6" t="str"/>
+      <x:c r="F62" s="6"/>
       <x:c r="G62" s="7" t="str">
         <x:v>Clean, refreshing lager/blond/wheat profile; NRG's Crisp family.</x:v>
       </x:c>
@@ -2203,7 +2203,7 @@
       <x:c r="E63" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F63" s="6" t="str"/>
+      <x:c r="F63" s="6"/>
       <x:c r="G63" s="7" t="str">
         <x:v>Acidity, Brett, mixed/spontaneous fermentation, or lambic character defines the style.</x:v>
       </x:c>
@@ -2224,20 +2224,20 @@
       <x:c r="E64" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F64" s="6" t="str"/>
+      <x:c r="F64" s="6"/>
       <x:c r="G64" s="7" t="str">
         <x:v>Clean, refreshing lager/blond/wheat profile; NRG's Crisp family.</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="34" customHeight="1">
       <x:c r="A65" s="4" t="str">
-        <x:v>Old / Stock Ale</x:v>
+        <x:v>Mild - Other</x:v>
       </x:c>
       <x:c r="B65" s="4" t="str">
         <x:v>Malt</x:v>
       </x:c>
       <x:c r="C65" s="5" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D65" s="6" t="str">
         <x:v>Yes</x:v>
@@ -2245,106 +2245,106 @@
       <x:c r="E65" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F65" s="6" t="str"/>
+      <x:c r="F65" s="6"/>
       <x:c r="G65" s="7" t="str">
-        <x:v>Toasty, nutty, caramel, or toffee-led profile; NRG's Malt family.</x:v>
+        <x:v>Classic English mild led by toasted biscuit, caramelized malt, and cocoa; NRG's Malt family.</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="34" customHeight="1">
       <x:c r="A66" s="4" t="str">
-        <x:v>Old Ale</x:v>
+        <x:v>Old / Stock Ale</x:v>
       </x:c>
       <x:c r="B66" s="4" t="str">
         <x:v>Malt</x:v>
       </x:c>
       <x:c r="C66" s="5" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D66" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="E66" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F66" s="6" t="str"/>
+      <x:c r="F66" s="6"/>
       <x:c r="G66" s="7" t="str">
         <x:v>Toasty, nutty, caramel, or toffee-led profile; NRG's Malt family.</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="34" customHeight="1">
       <x:c r="A67" s="4" t="str">
-        <x:v>Pale Ale - American</x:v>
+        <x:v>Old Ale</x:v>
       </x:c>
       <x:c r="B67" s="4" t="str">
-        <x:v>Hop</x:v>
+        <x:v>Malt</x:v>
       </x:c>
       <x:c r="C67" s="5" t="n">
-        <x:v>19</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D67" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="E67" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F67" s="6" t="str"/>
+      <x:c r="F67" s="6"/>
       <x:c r="G67" s="7" t="str">
-        <x:v>Hop aroma or bitterness is the defining flavor; NRG's Hop family.</x:v>
+        <x:v>Toasty, nutty, caramel, or toffee-led profile; NRG's Malt family.</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="34" customHeight="1">
       <x:c r="A68" s="4" t="str">
-        <x:v>Pale Ale - Belgian</x:v>
+        <x:v>Pale Ale - American</x:v>
       </x:c>
       <x:c r="B68" s="4" t="str">
-        <x:v>Malt</x:v>
+        <x:v>Hop</x:v>
       </x:c>
       <x:c r="C68" s="5" t="n">
-        <x:v>2</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D68" s="6" t="str">
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="E68" s="6" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="F68" s="6" t="str">
-        <x:v>Fruit &amp; Spice</x:v>
-      </x:c>
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F68" s="6"/>
       <x:c r="G68" s="7" t="str">
-        <x:v>Greg Engert's guide lists Belgian pale ale under Malt; current yeast-forward examples also appear in Fruit &amp; Spice.</x:v>
+        <x:v>Hop aroma or bitterness is the defining flavor; NRG's Hop family.</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="34" customHeight="1">
       <x:c r="A69" s="4" t="str">
-        <x:v>Pale Ale - Fruited</x:v>
+        <x:v>Pale Ale - Belgian</x:v>
       </x:c>
       <x:c r="B69" s="4" t="str">
-        <x:v>Hop</x:v>
+        <x:v>Malt</x:v>
       </x:c>
       <x:c r="C69" s="5" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D69" s="6" t="str">
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="E69" s="6" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="F69" s="6" t="str"/>
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F69" s="6" t="str">
+        <x:v>Fruit &amp; Spice</x:v>
+      </x:c>
       <x:c r="G69" s="7" t="str">
-        <x:v>Hop aroma or bitterness is the defining flavor; NRG's Hop family.</x:v>
+        <x:v>Greg Engert's guide lists Belgian pale ale under Malt; current yeast-forward examples also appear in Fruit &amp; Spice.</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="34" customHeight="1">
       <x:c r="A70" s="4" t="str">
-        <x:v>Pale Ale - New England / Hazy</x:v>
+        <x:v>Pale Ale - Fruited</x:v>
       </x:c>
       <x:c r="B70" s="4" t="str">
         <x:v>Hop</x:v>
       </x:c>
       <x:c r="C70" s="5" t="n">
-        <x:v>18</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D70" s="6" t="str">
         <x:v>Yes</x:v>
@@ -2352,20 +2352,20 @@
       <x:c r="E70" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F70" s="6" t="str"/>
+      <x:c r="F70" s="6"/>
       <x:c r="G70" s="7" t="str">
         <x:v>Hop aroma or bitterness is the defining flavor; NRG's Hop family.</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="34" customHeight="1">
       <x:c r="A71" s="4" t="str">
-        <x:v>Pale Ale - New Zealand</x:v>
+        <x:v>Pale Ale - New England / Hazy</x:v>
       </x:c>
       <x:c r="B71" s="4" t="str">
         <x:v>Hop</x:v>
       </x:c>
       <x:c r="C71" s="5" t="n">
-        <x:v>2</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D71" s="6" t="str">
         <x:v>Yes</x:v>
@@ -2373,17 +2373,17 @@
       <x:c r="E71" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F71" s="6" t="str"/>
+      <x:c r="F71" s="6"/>
       <x:c r="G71" s="7" t="str">
         <x:v>Hop aroma or bitterness is the defining flavor; NRG's Hop family.</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="34" customHeight="1">
       <x:c r="A72" s="4" t="str">
-        <x:v>Pilsner - American</x:v>
+        <x:v>Pale Ale - New Zealand</x:v>
       </x:c>
       <x:c r="B72" s="4" t="str">
-        <x:v>Crisp</x:v>
+        <x:v>Hop</x:v>
       </x:c>
       <x:c r="C72" s="5" t="n">
         <x:v>2</x:v>
@@ -2394,20 +2394,20 @@
       <x:c r="E72" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F72" s="6" t="str"/>
+      <x:c r="F72" s="6"/>
       <x:c r="G72" s="7" t="str">
-        <x:v>Clean, refreshing lager/blond/wheat profile; NRG's Crisp family.</x:v>
+        <x:v>Hop aroma or bitterness is the defining flavor; NRG's Hop family.</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="34" customHeight="1">
       <x:c r="A73" s="4" t="str">
-        <x:v>Pilsner - Czech / Bohemian</x:v>
+        <x:v>Pilsner - American</x:v>
       </x:c>
       <x:c r="B73" s="4" t="str">
         <x:v>Crisp</x:v>
       </x:c>
       <x:c r="C73" s="5" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D73" s="6" t="str">
         <x:v>Yes</x:v>
@@ -2415,20 +2415,20 @@
       <x:c r="E73" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F73" s="6" t="str"/>
+      <x:c r="F73" s="6"/>
       <x:c r="G73" s="7" t="str">
         <x:v>Clean, refreshing lager/blond/wheat profile; NRG's Crisp family.</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="34" customHeight="1">
       <x:c r="A74" s="4" t="str">
-        <x:v>Pilsner - German</x:v>
+        <x:v>Pilsner - Czech / Bohemian</x:v>
       </x:c>
       <x:c r="B74" s="4" t="str">
         <x:v>Crisp</x:v>
       </x:c>
       <x:c r="C74" s="5" t="n">
-        <x:v>11</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D74" s="6" t="str">
         <x:v>Yes</x:v>
@@ -2436,20 +2436,20 @@
       <x:c r="E74" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F74" s="6" t="str"/>
+      <x:c r="F74" s="6"/>
       <x:c r="G74" s="7" t="str">
         <x:v>Clean, refreshing lager/blond/wheat profile; NRG's Crisp family.</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="34" customHeight="1">
       <x:c r="A75" s="4" t="str">
-        <x:v>Pilsner - Italian</x:v>
+        <x:v>Pilsner - German</x:v>
       </x:c>
       <x:c r="B75" s="4" t="str">
         <x:v>Crisp</x:v>
       </x:c>
       <x:c r="C75" s="5" t="n">
-        <x:v>4</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D75" s="6" t="str">
         <x:v>Yes</x:v>
@@ -2457,20 +2457,20 @@
       <x:c r="E75" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F75" s="6" t="str"/>
+      <x:c r="F75" s="6"/>
       <x:c r="G75" s="7" t="str">
         <x:v>Clean, refreshing lager/blond/wheat profile; NRG's Crisp family.</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="34" customHeight="1">
       <x:c r="A76" s="4" t="str">
-        <x:v>Pilsner - Other</x:v>
+        <x:v>Pilsner - Italian</x:v>
       </x:c>
       <x:c r="B76" s="4" t="str">
         <x:v>Crisp</x:v>
       </x:c>
       <x:c r="C76" s="5" t="n">
-        <x:v>9</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D76" s="6" t="str">
         <x:v>Yes</x:v>
@@ -2478,20 +2478,20 @@
       <x:c r="E76" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F76" s="6" t="str"/>
+      <x:c r="F76" s="6"/>
       <x:c r="G76" s="7" t="str">
         <x:v>Clean, refreshing lager/blond/wheat profile; NRG's Crisp family.</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="34" customHeight="1">
       <x:c r="A77" s="4" t="str">
-        <x:v>Porter - American</x:v>
+        <x:v>Pilsner - Other</x:v>
       </x:c>
       <x:c r="B77" s="4" t="str">
-        <x:v>Roast</x:v>
+        <x:v>Crisp</x:v>
       </x:c>
       <x:c r="C77" s="5" t="n">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D77" s="6" t="str">
         <x:v>Yes</x:v>
@@ -2499,20 +2499,20 @@
       <x:c r="E77" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F77" s="6" t="str"/>
+      <x:c r="F77" s="6"/>
       <x:c r="G77" s="7" t="str">
-        <x:v>Dark malt, cocoa, coffee, or char-led profile; NRG's Roast family.</x:v>
+        <x:v>Clean, refreshing lager/blond/wheat profile; NRG's Crisp family.</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="34" customHeight="1">
       <x:c r="A78" s="4" t="str">
-        <x:v>Porter - Baltic</x:v>
+        <x:v>Porter - American</x:v>
       </x:c>
       <x:c r="B78" s="4" t="str">
         <x:v>Roast</x:v>
       </x:c>
       <x:c r="C78" s="5" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D78" s="6" t="str">
         <x:v>Yes</x:v>
@@ -2520,14 +2520,14 @@
       <x:c r="E78" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F78" s="6" t="str"/>
+      <x:c r="F78" s="6"/>
       <x:c r="G78" s="7" t="str">
         <x:v>Dark malt, cocoa, coffee, or char-led profile; NRG's Roast family.</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="34" customHeight="1">
       <x:c r="A79" s="4" t="str">
-        <x:v>Porter - Other</x:v>
+        <x:v>Porter - Baltic</x:v>
       </x:c>
       <x:c r="B79" s="4" t="str">
         <x:v>Roast</x:v>
@@ -2541,17 +2541,17 @@
       <x:c r="E79" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F79" s="6" t="str"/>
+      <x:c r="F79" s="6"/>
       <x:c r="G79" s="7" t="str">
         <x:v>Dark malt, cocoa, coffee, or char-led profile; NRG's Roast family.</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="34" customHeight="1">
       <x:c r="A80" s="4" t="str">
-        <x:v>Porter - Smoked</x:v>
+        <x:v>Porter - Other</x:v>
       </x:c>
       <x:c r="B80" s="4" t="str">
-        <x:v>Smoke</x:v>
+        <x:v>Roast</x:v>
       </x:c>
       <x:c r="C80" s="5" t="n">
         <x:v>1</x:v>
@@ -2562,17 +2562,17 @@
       <x:c r="E80" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F80" s="6" t="str"/>
+      <x:c r="F80" s="6"/>
       <x:c r="G80" s="7" t="str">
-        <x:v>Smoked malt is style-defining; NRG's Smoke family.</x:v>
+        <x:v>Dark malt, cocoa, coffee, or char-led profile; NRG's Roast family.</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="34" customHeight="1">
       <x:c r="A81" s="4" t="str">
-        <x:v>Pumpkin / Yam Beer</x:v>
+        <x:v>Porter - Smoked</x:v>
       </x:c>
       <x:c r="B81" s="4" t="str">
-        <x:v>Fruit &amp; Spice</x:v>
+        <x:v>Smoke</x:v>
       </x:c>
       <x:c r="C81" s="5" t="n">
         <x:v>1</x:v>
@@ -2583,20 +2583,20 @@
       <x:c r="E81" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F81" s="6" t="str"/>
+      <x:c r="F81" s="6"/>
       <x:c r="G81" s="7" t="str">
-        <x:v>Fermentation- or ingredient-led fruit/spice without sourness as the defining trait.</x:v>
+        <x:v>Smoked malt is style-defining; NRG's Smoke family.</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="34" customHeight="1">
       <x:c r="A82" s="4" t="str">
-        <x:v>Rauchbier</x:v>
+        <x:v>Pumpkin / Yam Beer</x:v>
       </x:c>
       <x:c r="B82" s="4" t="str">
-        <x:v>Smoke</x:v>
+        <x:v>Fruit &amp; Spice</x:v>
       </x:c>
       <x:c r="C82" s="5" t="n">
-        <x:v>16</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D82" s="6" t="str">
         <x:v>Yes</x:v>
@@ -2604,20 +2604,20 @@
       <x:c r="E82" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F82" s="6" t="str"/>
+      <x:c r="F82" s="6"/>
       <x:c r="G82" s="7" t="str">
-        <x:v>Smoked malt is style-defining; NRG's Smoke family.</x:v>
+        <x:v>Fermentation- or ingredient-led fruit/spice without sourness as the defining trait.</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="34" customHeight="1">
       <x:c r="A83" s="4" t="str">
-        <x:v>Red Ale - Ambrée</x:v>
+        <x:v>Rauchbier</x:v>
       </x:c>
       <x:c r="B83" s="4" t="str">
-        <x:v>Malt</x:v>
+        <x:v>Smoke</x:v>
       </x:c>
       <x:c r="C83" s="5" t="n">
-        <x:v>1</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D83" s="6" t="str">
         <x:v>Yes</x:v>
@@ -2625,41 +2625,41 @@
       <x:c r="E83" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F83" s="6" t="str"/>
+      <x:c r="F83" s="6"/>
       <x:c r="G83" s="7" t="str">
-        <x:v>Toasty, nutty, caramel, or toffee-led profile; NRG's Malt family.</x:v>
+        <x:v>Smoked malt is style-defining; NRG's Smoke family.</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="34" customHeight="1">
       <x:c r="A84" s="4" t="str">
-        <x:v>Red Ale - American Amber / Red</x:v>
+        <x:v>Red Ale - Ambrée</x:v>
       </x:c>
       <x:c r="B84" s="4" t="str">
-        <x:v>Hop</x:v>
+        <x:v>Malt</x:v>
       </x:c>
       <x:c r="C84" s="5" t="n">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D84" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="E84" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F84" s="6" t="str"/>
+      <x:c r="F84" s="6"/>
       <x:c r="G84" s="7" t="str">
-        <x:v>Hop aroma or bitterness is the defining flavor; NRG's Hop family.</x:v>
+        <x:v>Toasty, nutty, caramel, or toffee-led profile; NRG's Malt family.</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="34" customHeight="1">
       <x:c r="A85" s="4" t="str">
-        <x:v>Red Ale - Irish</x:v>
+        <x:v>Red Ale - American Amber / Red</x:v>
       </x:c>
       <x:c r="B85" s="4" t="str">
-        <x:v>Malt</x:v>
+        <x:v>Hop</x:v>
       </x:c>
       <x:c r="C85" s="5" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D85" s="6" t="str">
         <x:v>Yes</x:v>
@@ -2667,20 +2667,20 @@
       <x:c r="E85" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F85" s="6" t="str"/>
+      <x:c r="F85" s="6"/>
       <x:c r="G85" s="7" t="str">
-        <x:v>Toasty, nutty, caramel, or toffee-led profile; NRG's Malt family.</x:v>
+        <x:v>Hop aroma or bitterness is the defining flavor; NRG's Hop family.</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="34" customHeight="1">
       <x:c r="A86" s="4" t="str">
-        <x:v>Schwarzbier</x:v>
+        <x:v>Red Ale - Irish</x:v>
       </x:c>
       <x:c r="B86" s="4" t="str">
-        <x:v>Roast</x:v>
+        <x:v>Malt</x:v>
       </x:c>
       <x:c r="C86" s="5" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D86" s="6" t="str">
         <x:v>Yes</x:v>
@@ -2688,20 +2688,20 @@
       <x:c r="E86" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F86" s="6" t="str"/>
+      <x:c r="F86" s="6"/>
       <x:c r="G86" s="7" t="str">
-        <x:v>Dark malt, cocoa, coffee, or char-led profile; NRG's Roast family.</x:v>
+        <x:v>Toasty, nutty, caramel, or toffee-led profile; NRG's Malt family.</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="34" customHeight="1">
       <x:c r="A87" s="4" t="str">
-        <x:v>Scotch Ale / Wee Heavy</x:v>
+        <x:v>Schwarzbier</x:v>
       </x:c>
       <x:c r="B87" s="4" t="str">
-        <x:v>Malt</x:v>
+        <x:v>Roast</x:v>
       </x:c>
       <x:c r="C87" s="5" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D87" s="6" t="str">
         <x:v>Yes</x:v>
@@ -2709,17 +2709,17 @@
       <x:c r="E87" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F87" s="6" t="str"/>
+      <x:c r="F87" s="6"/>
       <x:c r="G87" s="7" t="str">
-        <x:v>Toasty, nutty, caramel, or toffee-led profile; NRG's Malt family.</x:v>
+        <x:v>Dark malt, cocoa, coffee, or char-led profile; NRG's Roast family.</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="34" customHeight="1">
       <x:c r="A88" s="4" t="str">
-        <x:v>Smoked Beer</x:v>
+        <x:v>Scotch Ale / Wee Heavy</x:v>
       </x:c>
       <x:c r="B88" s="4" t="str">
-        <x:v>Smoke</x:v>
+        <x:v>Malt</x:v>
       </x:c>
       <x:c r="C88" s="5" t="n">
         <x:v>1</x:v>
@@ -2730,20 +2730,20 @@
       <x:c r="E88" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F88" s="6" t="str"/>
+      <x:c r="F88" s="6"/>
       <x:c r="G88" s="7" t="str">
-        <x:v>Smoked malt is style-defining; NRG's Smoke family.</x:v>
+        <x:v>Toasty, nutty, caramel, or toffee-led profile; NRG's Malt family.</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="34" customHeight="1">
       <x:c r="A89" s="4" t="str">
-        <x:v>Sour - Berliner Weisse</x:v>
+        <x:v>Smoked Beer</x:v>
       </x:c>
       <x:c r="B89" s="4" t="str">
-        <x:v>Tart &amp; Funky</x:v>
+        <x:v>Smoke</x:v>
       </x:c>
       <x:c r="C89" s="5" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D89" s="6" t="str">
         <x:v>Yes</x:v>
@@ -2751,14 +2751,14 @@
       <x:c r="E89" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F89" s="6" t="str"/>
+      <x:c r="F89" s="6"/>
       <x:c r="G89" s="7" t="str">
-        <x:v>Acidity, Brett, mixed/spontaneous fermentation, or lambic character defines the style.</x:v>
+        <x:v>Smoked malt is style-defining; NRG's Smoke family.</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="34" customHeight="1">
       <x:c r="A90" s="4" t="str">
-        <x:v>Sour - Flanders Red Ale</x:v>
+        <x:v>Sour - Berliner Weisse</x:v>
       </x:c>
       <x:c r="B90" s="4" t="str">
         <x:v>Tart &amp; Funky</x:v>
@@ -2772,20 +2772,20 @@
       <x:c r="E90" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F90" s="6" t="str"/>
+      <x:c r="F90" s="6"/>
       <x:c r="G90" s="7" t="str">
         <x:v>Acidity, Brett, mixed/spontaneous fermentation, or lambic character defines the style.</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="34" customHeight="1">
       <x:c r="A91" s="4" t="str">
-        <x:v>Sour - Fruited</x:v>
+        <x:v>Sour - Flanders Red Ale</x:v>
       </x:c>
       <x:c r="B91" s="4" t="str">
         <x:v>Tart &amp; Funky</x:v>
       </x:c>
       <x:c r="C91" s="5" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D91" s="6" t="str">
         <x:v>Yes</x:v>
@@ -2793,20 +2793,20 @@
       <x:c r="E91" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F91" s="6" t="str"/>
+      <x:c r="F91" s="6"/>
       <x:c r="G91" s="7" t="str">
         <x:v>Acidity, Brett, mixed/spontaneous fermentation, or lambic character defines the style.</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="34" customHeight="1">
       <x:c r="A92" s="4" t="str">
-        <x:v>Sour - Fruited Berliner Weisse</x:v>
+        <x:v>Sour - Fruited</x:v>
       </x:c>
       <x:c r="B92" s="4" t="str">
         <x:v>Tart &amp; Funky</x:v>
       </x:c>
       <x:c r="C92" s="5" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D92" s="6" t="str">
         <x:v>Yes</x:v>
@@ -2814,20 +2814,20 @@
       <x:c r="E92" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F92" s="6" t="str"/>
+      <x:c r="F92" s="6"/>
       <x:c r="G92" s="7" t="str">
         <x:v>Acidity, Brett, mixed/spontaneous fermentation, or lambic character defines the style.</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="34" customHeight="1">
       <x:c r="A93" s="4" t="str">
-        <x:v>Sour - Fruited Gose</x:v>
+        <x:v>Sour - Fruited Berliner Weisse</x:v>
       </x:c>
       <x:c r="B93" s="4" t="str">
         <x:v>Tart &amp; Funky</x:v>
       </x:c>
       <x:c r="C93" s="5" t="n">
-        <x:v>9</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D93" s="6" t="str">
         <x:v>Yes</x:v>
@@ -2835,20 +2835,20 @@
       <x:c r="E93" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F93" s="6" t="str"/>
+      <x:c r="F93" s="6"/>
       <x:c r="G93" s="7" t="str">
         <x:v>Acidity, Brett, mixed/spontaneous fermentation, or lambic character defines the style.</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="34" customHeight="1">
       <x:c r="A94" s="4" t="str">
-        <x:v>Sour - Other</x:v>
+        <x:v>Sour - Fruited Gose</x:v>
       </x:c>
       <x:c r="B94" s="4" t="str">
         <x:v>Tart &amp; Funky</x:v>
       </x:c>
       <x:c r="C94" s="5" t="n">
-        <x:v>1</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D94" s="6" t="str">
         <x:v>Yes</x:v>
@@ -2856,17 +2856,17 @@
       <x:c r="E94" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F94" s="6" t="str"/>
+      <x:c r="F94" s="6"/>
       <x:c r="G94" s="7" t="str">
         <x:v>Acidity, Brett, mixed/spontaneous fermentation, or lambic character defines the style.</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="34" customHeight="1">
       <x:c r="A95" s="4" t="str">
-        <x:v>Stout - American</x:v>
+        <x:v>Sour - Other</x:v>
       </x:c>
       <x:c r="B95" s="4" t="str">
-        <x:v>Roast</x:v>
+        <x:v>Tart &amp; Funky</x:v>
       </x:c>
       <x:c r="C95" s="5" t="n">
         <x:v>1</x:v>
@@ -2877,14 +2877,14 @@
       <x:c r="E95" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F95" s="6" t="str"/>
+      <x:c r="F95" s="6"/>
       <x:c r="G95" s="7" t="str">
-        <x:v>Dark malt, cocoa, coffee, or char-led profile; NRG's Roast family.</x:v>
+        <x:v>Acidity, Brett, mixed/spontaneous fermentation, or lambic character defines the style.</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="34" customHeight="1">
       <x:c r="A96" s="4" t="str">
-        <x:v>Stout - Coffee</x:v>
+        <x:v>Stout - American</x:v>
       </x:c>
       <x:c r="B96" s="4" t="str">
         <x:v>Roast</x:v>
@@ -2898,20 +2898,20 @@
       <x:c r="E96" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F96" s="6" t="str"/>
+      <x:c r="F96" s="6"/>
       <x:c r="G96" s="7" t="str">
         <x:v>Dark malt, cocoa, coffee, or char-led profile; NRG's Roast family.</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="34" customHeight="1">
       <x:c r="A97" s="4" t="str">
-        <x:v>Stout - English</x:v>
+        <x:v>Stout - Coffee</x:v>
       </x:c>
       <x:c r="B97" s="4" t="str">
         <x:v>Roast</x:v>
       </x:c>
       <x:c r="C97" s="5" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D97" s="6" t="str">
         <x:v>Yes</x:v>
@@ -2919,14 +2919,14 @@
       <x:c r="E97" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F97" s="6" t="str"/>
+      <x:c r="F97" s="6"/>
       <x:c r="G97" s="7" t="str">
         <x:v>Dark malt, cocoa, coffee, or char-led profile; NRG's Roast family.</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="34" customHeight="1">
       <x:c r="A98" s="4" t="str">
-        <x:v>Stout - Foreign / Export</x:v>
+        <x:v>Stout - English</x:v>
       </x:c>
       <x:c r="B98" s="4" t="str">
         <x:v>Roast</x:v>
@@ -2940,20 +2940,20 @@
       <x:c r="E98" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F98" s="6" t="str"/>
+      <x:c r="F98" s="6"/>
       <x:c r="G98" s="7" t="str">
         <x:v>Dark malt, cocoa, coffee, or char-led profile; NRG's Roast family.</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="34" customHeight="1">
       <x:c r="A99" s="4" t="str">
-        <x:v>Stout - Imperial / Double</x:v>
+        <x:v>Stout - Foreign / Export</x:v>
       </x:c>
       <x:c r="B99" s="4" t="str">
         <x:v>Roast</x:v>
       </x:c>
       <x:c r="C99" s="5" t="n">
-        <x:v>9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D99" s="6" t="str">
         <x:v>Yes</x:v>
@@ -2961,20 +2961,20 @@
       <x:c r="E99" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F99" s="6" t="str"/>
+      <x:c r="F99" s="6"/>
       <x:c r="G99" s="7" t="str">
         <x:v>Dark malt, cocoa, coffee, or char-led profile; NRG's Roast family.</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="34" customHeight="1">
       <x:c r="A100" s="4" t="str">
-        <x:v>Stout - Imperial / Double Coffee</x:v>
+        <x:v>Stout - Imperial / Double</x:v>
       </x:c>
       <x:c r="B100" s="4" t="str">
         <x:v>Roast</x:v>
       </x:c>
       <x:c r="C100" s="5" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D100" s="6" t="str">
         <x:v>Yes</x:v>
@@ -2982,20 +2982,20 @@
       <x:c r="E100" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F100" s="6" t="str"/>
+      <x:c r="F100" s="6"/>
       <x:c r="G100" s="7" t="str">
         <x:v>Dark malt, cocoa, coffee, or char-led profile; NRG's Roast family.</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="34" customHeight="1">
       <x:c r="A101" s="4" t="str">
-        <x:v>Stout - Imperial / Double Milk</x:v>
+        <x:v>Stout - Imperial / Double Coffee</x:v>
       </x:c>
       <x:c r="B101" s="4" t="str">
         <x:v>Roast</x:v>
       </x:c>
       <x:c r="C101" s="5" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D101" s="6" t="str">
         <x:v>Yes</x:v>
@@ -3003,20 +3003,20 @@
       <x:c r="E101" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F101" s="6" t="str"/>
+      <x:c r="F101" s="6"/>
       <x:c r="G101" s="7" t="str">
         <x:v>Dark malt, cocoa, coffee, or char-led profile; NRG's Roast family.</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="34" customHeight="1">
       <x:c r="A102" s="4" t="str">
-        <x:v>Stout - Imperial / Double Pastry</x:v>
+        <x:v>Stout - Imperial / Double Milk</x:v>
       </x:c>
       <x:c r="B102" s="4" t="str">
         <x:v>Roast</x:v>
       </x:c>
       <x:c r="C102" s="5" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D102" s="6" t="str">
         <x:v>Yes</x:v>
@@ -3024,20 +3024,20 @@
       <x:c r="E102" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F102" s="6" t="str"/>
+      <x:c r="F102" s="6"/>
       <x:c r="G102" s="7" t="str">
         <x:v>Dark malt, cocoa, coffee, or char-led profile; NRG's Roast family.</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="34" customHeight="1">
       <x:c r="A103" s="4" t="str">
-        <x:v>Stout - Irish Dry</x:v>
+        <x:v>Stout - Imperial / Double Pastry</x:v>
       </x:c>
       <x:c r="B103" s="4" t="str">
         <x:v>Roast</x:v>
       </x:c>
       <x:c r="C103" s="5" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D103" s="6" t="str">
         <x:v>Yes</x:v>
@@ -3045,20 +3045,20 @@
       <x:c r="E103" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F103" s="6" t="str"/>
+      <x:c r="F103" s="6"/>
       <x:c r="G103" s="7" t="str">
         <x:v>Dark malt, cocoa, coffee, or char-led profile; NRG's Roast family.</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="34" customHeight="1">
       <x:c r="A104" s="4" t="str">
-        <x:v>Stout - Milk / Sweet</x:v>
+        <x:v>Stout - Irish Dry</x:v>
       </x:c>
       <x:c r="B104" s="4" t="str">
         <x:v>Roast</x:v>
       </x:c>
       <x:c r="C104" s="5" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D104" s="6" t="str">
         <x:v>Yes</x:v>
@@ -3066,20 +3066,20 @@
       <x:c r="E104" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F104" s="6" t="str"/>
+      <x:c r="F104" s="6"/>
       <x:c r="G104" s="7" t="str">
         <x:v>Dark malt, cocoa, coffee, or char-led profile; NRG's Roast family.</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="34" customHeight="1">
       <x:c r="A105" s="4" t="str">
-        <x:v>Stout - Oatmeal</x:v>
+        <x:v>Stout - Milk / Sweet</x:v>
       </x:c>
       <x:c r="B105" s="4" t="str">
         <x:v>Roast</x:v>
       </x:c>
       <x:c r="C105" s="5" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D105" s="6" t="str">
         <x:v>Yes</x:v>
@@ -3087,14 +3087,14 @@
       <x:c r="E105" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F105" s="6" t="str"/>
+      <x:c r="F105" s="6"/>
       <x:c r="G105" s="7" t="str">
         <x:v>Dark malt, cocoa, coffee, or char-led profile; NRG's Roast family.</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="34" customHeight="1">
       <x:c r="A106" s="4" t="str">
-        <x:v>Stout - Russian Imperial</x:v>
+        <x:v>Stout - Oatmeal</x:v>
       </x:c>
       <x:c r="B106" s="4" t="str">
         <x:v>Roast</x:v>
@@ -3108,40 +3108,38 @@
       <x:c r="E106" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F106" s="6" t="str"/>
+      <x:c r="F106" s="6"/>
       <x:c r="G106" s="7" t="str">
         <x:v>Dark malt, cocoa, coffee, or char-led profile; NRG's Roast family.</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="34" customHeight="1">
       <x:c r="A107" s="4" t="str">
-        <x:v>Table Beer</x:v>
+        <x:v>Stout - Russian Imperial</x:v>
       </x:c>
       <x:c r="B107" s="4" t="str">
-        <x:v>Tart &amp; Funky</x:v>
+        <x:v>Roast</x:v>
       </x:c>
       <x:c r="C107" s="5" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D107" s="6" t="str">
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="E107" s="6" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="F107" s="6" t="str">
-        <x:v>Fruit &amp; Spice</x:v>
-      </x:c>
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F107" s="6"/>
       <x:c r="G107" s="7" t="str">
-        <x:v>Current ChurchKey menus place mixed-fermentation table beer under Tart &amp; Funky; clean Belgian table beer can be Fruit &amp; Spice.</x:v>
+        <x:v>Dark malt, cocoa, coffee, or char-led profile; NRG's Roast family.</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="34" customHeight="1">
       <x:c r="A108" s="4" t="str">
-        <x:v>Wheat Beer - American Pale Wheat</x:v>
+        <x:v>Table Beer</x:v>
       </x:c>
       <x:c r="B108" s="4" t="str">
-        <x:v>Crisp</x:v>
+        <x:v>Tart &amp; Funky</x:v>
       </x:c>
       <x:c r="C108" s="5" t="n">
         <x:v>2</x:v>
@@ -3150,22 +3148,24 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="E108" s="6" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="F108" s="6" t="str"/>
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F108" s="6" t="str">
+        <x:v>Fruit &amp; Spice</x:v>
+      </x:c>
       <x:c r="G108" s="7" t="str">
-        <x:v>Clean, refreshing lager/blond/wheat profile; NRG's Crisp family.</x:v>
+        <x:v>Current ChurchKey menus place mixed-fermentation table beer under Tart &amp; Funky; clean Belgian table beer can be Fruit &amp; Spice.</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="34" customHeight="1">
       <x:c r="A109" s="4" t="str">
-        <x:v>Wheat Beer - Hefeweizen</x:v>
+        <x:v>Wheat Beer - American Pale Wheat</x:v>
       </x:c>
       <x:c r="B109" s="4" t="str">
-        <x:v>Fruit &amp; Spice</x:v>
+        <x:v>Crisp</x:v>
       </x:c>
       <x:c r="C109" s="5" t="n">
-        <x:v>10</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D109" s="6" t="str">
         <x:v>Yes</x:v>
@@ -3173,20 +3173,20 @@
       <x:c r="E109" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F109" s="6" t="str"/>
+      <x:c r="F109" s="6"/>
       <x:c r="G109" s="7" t="str">
-        <x:v>Fermentation- or ingredient-led fruit/spice without sourness as the defining trait.</x:v>
+        <x:v>Clean, refreshing lager/blond/wheat profile; NRG's Crisp family.</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="34" customHeight="1">
       <x:c r="A110" s="4" t="str">
-        <x:v>Wheat Beer - Kristallweizen</x:v>
+        <x:v>Wheat Beer - Hefeweizen</x:v>
       </x:c>
       <x:c r="B110" s="4" t="str">
         <x:v>Fruit &amp; Spice</x:v>
       </x:c>
       <x:c r="C110" s="5" t="n">
-        <x:v>1</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D110" s="6" t="str">
         <x:v>Yes</x:v>
@@ -3194,20 +3194,20 @@
       <x:c r="E110" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F110" s="6" t="str"/>
+      <x:c r="F110" s="6"/>
       <x:c r="G110" s="7" t="str">
         <x:v>Fermentation- or ingredient-led fruit/spice without sourness as the defining trait.</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="34" customHeight="1">
       <x:c r="A111" s="4" t="str">
-        <x:v>Wheat Beer - Witbier / Blanche</x:v>
+        <x:v>Wheat Beer - Kristallweizen</x:v>
       </x:c>
       <x:c r="B111" s="4" t="str">
         <x:v>Fruit &amp; Spice</x:v>
       </x:c>
       <x:c r="C111" s="5" t="n">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D111" s="6" t="str">
         <x:v>Yes</x:v>
@@ -3215,20 +3215,20 @@
       <x:c r="E111" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F111" s="6" t="str"/>
+      <x:c r="F111" s="6"/>
       <x:c r="G111" s="7" t="str">
         <x:v>Fermentation- or ingredient-led fruit/spice without sourness as the defining trait.</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="34" customHeight="1">
       <x:c r="A112" s="4" t="str">
-        <x:v>Wild Ale - American</x:v>
+        <x:v>Wheat Beer - Witbier / Blanche</x:v>
       </x:c>
       <x:c r="B112" s="4" t="str">
-        <x:v>Tart &amp; Funky</x:v>
+        <x:v>Fruit &amp; Spice</x:v>
       </x:c>
       <x:c r="C112" s="5" t="n">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D112" s="6" t="str">
         <x:v>Yes</x:v>
@@ -3236,20 +3236,20 @@
       <x:c r="E112" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F112" s="6" t="str"/>
+      <x:c r="F112" s="6"/>
       <x:c r="G112" s="7" t="str">
-        <x:v>Acidity, Brett, mixed/spontaneous fermentation, or lambic character defines the style.</x:v>
+        <x:v>Fermentation- or ingredient-led fruit/spice without sourness as the defining trait.</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="34" customHeight="1">
       <x:c r="A113" s="4" t="str">
-        <x:v>Wild Ale - Other</x:v>
+        <x:v>Wild Ale - American</x:v>
       </x:c>
       <x:c r="B113" s="4" t="str">
         <x:v>Tart &amp; Funky</x:v>
       </x:c>
       <x:c r="C113" s="5" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D113" s="6" t="str">
         <x:v>Yes</x:v>
@@ -3257,31 +3257,52 @@
       <x:c r="E113" s="6" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F113" s="6" t="str"/>
+      <x:c r="F113" s="6"/>
       <x:c r="G113" s="7" t="str">
         <x:v>Acidity, Brett, mixed/spontaneous fermentation, or lambic character defines the style.</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="34" customHeight="1">
       <x:c r="A114" s="4" t="str">
+        <x:v>Wild Ale - Other</x:v>
+      </x:c>
+      <x:c r="B114" s="4" t="str">
+        <x:v>Tart &amp; Funky</x:v>
+      </x:c>
+      <x:c r="C114" s="5" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D114" s="6" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E114" s="6" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F114" s="6"/>
+      <x:c r="G114" s="7" t="str">
+        <x:v>Acidity, Brett, mixed/spontaneous fermentation, or lambic character defines the style.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" t="str">
         <x:v>Winter Ale</x:v>
       </x:c>
-      <x:c r="B114" s="4" t="str">
+      <x:c r="B115" t="str">
         <x:v>Fruit &amp; Spice</x:v>
       </x:c>
-      <x:c r="C114" s="5" t="n">
+      <x:c r="C115" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D114" s="6" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E114" s="6" t="str">
+      <x:c r="D115" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E115" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="F114" s="6" t="str">
+      <x:c r="F115" t="str">
         <x:v>Malt</x:v>
       </x:c>
-      <x:c r="G114" s="7" t="str">
+      <x:c r="G115" t="str">
         <x:v>Default follows NRG's spiced Belgian winter examples; unspiced, caramel-led winter ale belongs in Malt.</x:v>
       </x:c>
     </x:row>
@@ -3307,7 +3328,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37573c31e6e14ab8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ee538c0c5af4af7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4697,7 +4718,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb29065f208b04619"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8555bed7a6eb4ce0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4743,15 +4764,15 @@
         <x:v>Current styles mapped</x:v>
       </x:c>
       <x:c r="D2" s="29" t="n">
-        <x:f>COUNTIF('Crosswalk'!$D$2:$D$114,"Yes")</x:f>
+        <x:f>COUNTIF('Crosswalk'!$D$2:$D$115,"Yes")</x:f>
         <x:v>109</x:v>
       </x:c>
       <x:c r="E2" s="29" t="str">
         <x:v>Current beers covered</x:v>
       </x:c>
       <x:c r="F2" s="29" t="n">
-        <x:f>SUM('Crosswalk'!$C$2:$C$114)</x:f>
-        <x:v>607</x:v>
+        <x:f>SUM('Crosswalk'!$C$2:$C$115)</x:f>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="G2" s="29" t="str">
         <x:v>Beer-level reviews</x:v>
@@ -4811,24 +4832,24 @@
         <x:v>Blond ale, Kölsch, pale/amber lager, pilsner</x:v>
       </x:c>
       <x:c r="D5" s="62" t="n">
-        <x:f>COUNTIF('Crosswalk'!$B$2:$B$114,A5)</x:f>
+        <x:f>COUNTIF('Crosswalk'!$B$2:$B$115,A5)</x:f>
         <x:v>27</x:v>
       </x:c>
       <x:c r="E5" s="62" t="n">
-        <x:f>COUNTIFS('Crosswalk'!$B$2:$B$114,A5,'Crosswalk'!$D$2:$D$114,"Yes")</x:f>
+        <x:f>COUNTIFS('Crosswalk'!$B$2:$B$115,A5,'Crosswalk'!$D$2:$D$115,"Yes")</x:f>
         <x:v>26</x:v>
       </x:c>
       <x:c r="F5" s="62" t="n">
-        <x:f>SUMIF('Crosswalk'!$B$2:$B$114,A5,'Crosswalk'!$C$2:$C$114)</x:f>
-        <x:v>113</x:v>
+        <x:f>SUMIF('Crosswalk'!$B$2:$B$115,A5,'Crosswalk'!$C$2:$C$115)</x:f>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="G5" s="62" t="n">
         <x:f>F5+COUNTIF('Beer Review'!$E$2:$E$42,A5)-COUNTIF('Beer Review'!$D$2:$D$42,A5)</x:f>
-        <x:v>112</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H5" s="63" t="n">
         <x:f>G5/SUM($G$5:$G$11)</x:f>
-        <x:v>0.18451400329489293</x:v>
+        <x:v>0.18638573743922204</x:v>
       </x:c>
       <x:c r="I5" s="64" t="n">
         <x:f>G5-F5</x:f>
@@ -4849,24 +4870,24 @@
         <x:v>Pale ale, IPA, California common, American amber</x:v>
       </x:c>
       <x:c r="D6" s="62" t="n">
-        <x:f>COUNTIF('Crosswalk'!$B$2:$B$114,A6)</x:f>
+        <x:f>COUNTIF('Crosswalk'!$B$2:$B$115,A6)</x:f>
         <x:v>18</x:v>
       </x:c>
       <x:c r="E6" s="62" t="n">
-        <x:f>COUNTIFS('Crosswalk'!$B$2:$B$114,A6,'Crosswalk'!$D$2:$D$114,"Yes")</x:f>
+        <x:f>COUNTIFS('Crosswalk'!$B$2:$B$115,A6,'Crosswalk'!$D$2:$D$115,"Yes")</x:f>
         <x:v>18</x:v>
       </x:c>
       <x:c r="F6" s="62" t="n">
-        <x:f>SUMIF('Crosswalk'!$B$2:$B$114,A6,'Crosswalk'!$C$2:$C$114)</x:f>
-        <x:v>313</x:v>
+        <x:f>SUMIF('Crosswalk'!$B$2:$B$115,A6,'Crosswalk'!$C$2:$C$115)</x:f>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="G6" s="62" t="n">
         <x:f>F6+COUNTIF('Beer Review'!$E$2:$E$42,A6)-COUNTIF('Beer Review'!$D$2:$D$42,A6)</x:f>
-        <x:v>315</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="H6" s="63" t="n">
         <x:f>G6/SUM($G$5:$G$11)</x:f>
-        <x:v>0.5189456342668863</x:v>
+        <x:v>0.5186385737439222</x:v>
       </x:c>
       <x:c r="I6" s="64" t="n">
         <x:f>G6-F6</x:f>
@@ -4887,15 +4908,15 @@
         <x:v>Dunkel, doppelbock, ESB, Irish red, wee heavy</x:v>
       </x:c>
       <x:c r="D7" s="62" t="n">
-        <x:f>COUNTIF('Crosswalk'!$B$2:$B$114,A7)</x:f>
-        <x:v>13</x:v>
+        <x:f>COUNTIF('Crosswalk'!$B$2:$B$115,A7)</x:f>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E7" s="62" t="n">
-        <x:f>COUNTIFS('Crosswalk'!$B$2:$B$114,A7,'Crosswalk'!$D$2:$D$114,"Yes")</x:f>
+        <x:f>COUNTIFS('Crosswalk'!$B$2:$B$115,A7,'Crosswalk'!$D$2:$D$115,"Yes")</x:f>
         <x:v>11</x:v>
       </x:c>
       <x:c r="F7" s="62" t="n">
-        <x:f>SUMIF('Crosswalk'!$B$2:$B$114,A7,'Crosswalk'!$C$2:$C$114)</x:f>
+        <x:f>SUMIF('Crosswalk'!$B$2:$B$115,A7,'Crosswalk'!$C$2:$C$115)</x:f>
         <x:v>25</x:v>
       </x:c>
       <x:c r="G7" s="62" t="n">
@@ -4904,7 +4925,7 @@
       </x:c>
       <x:c r="H7" s="63" t="n">
         <x:f>G7/SUM($G$5:$G$11)</x:f>
-        <x:v>0.036243822075782535</x:v>
+        <x:v>0.03565640194489465</x:v>
       </x:c>
       <x:c r="I7" s="64" t="n">
         <x:f>G7-F7</x:f>
@@ -4925,15 +4946,15 @@
         <x:v>Porter, stout, schwarzbier, black IPA</x:v>
       </x:c>
       <x:c r="D8" s="62" t="n">
-        <x:f>COUNTIF('Crosswalk'!$B$2:$B$114,A8)</x:f>
+        <x:f>COUNTIF('Crosswalk'!$B$2:$B$115,A8)</x:f>
         <x:v>19</x:v>
       </x:c>
       <x:c r="E8" s="62" t="n">
-        <x:f>COUNTIFS('Crosswalk'!$B$2:$B$114,A8,'Crosswalk'!$D$2:$D$114,"Yes")</x:f>
+        <x:f>COUNTIFS('Crosswalk'!$B$2:$B$115,A8,'Crosswalk'!$D$2:$D$115,"Yes")</x:f>
         <x:v>19</x:v>
       </x:c>
       <x:c r="F8" s="62" t="n">
-        <x:f>SUMIF('Crosswalk'!$B$2:$B$114,A8,'Crosswalk'!$C$2:$C$114)</x:f>
+        <x:f>SUMIF('Crosswalk'!$B$2:$B$115,A8,'Crosswalk'!$C$2:$C$115)</x:f>
         <x:v>44</x:v>
       </x:c>
       <x:c r="G8" s="62" t="n">
@@ -4942,7 +4963,7 @@
       </x:c>
       <x:c r="H8" s="63" t="n">
         <x:f>G8/SUM($G$5:$G$11)</x:f>
-        <x:v>0.07248764415156507</x:v>
+        <x:v>0.0713128038897893</x:v>
       </x:c>
       <x:c r="I8" s="64" t="n">
         <x:f>G8-F8</x:f>
@@ -4963,24 +4984,24 @@
         <x:v>Rauchbier, Grodziskie, smoked lager/porter</x:v>
       </x:c>
       <x:c r="D9" s="62" t="n">
-        <x:f>COUNTIF('Crosswalk'!$B$2:$B$114,A9)</x:f>
+        <x:f>COUNTIF('Crosswalk'!$B$2:$B$115,A9)</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="E9" s="62" t="n">
-        <x:f>COUNTIFS('Crosswalk'!$B$2:$B$114,A9,'Crosswalk'!$D$2:$D$114,"Yes")</x:f>
+        <x:f>COUNTIFS('Crosswalk'!$B$2:$B$115,A9,'Crosswalk'!$D$2:$D$115,"Yes")</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="F9" s="62" t="n">
-        <x:f>SUMIF('Crosswalk'!$B$2:$B$114,A9,'Crosswalk'!$C$2:$C$114)</x:f>
-        <x:v>28</x:v>
+        <x:f>SUMIF('Crosswalk'!$B$2:$B$115,A9,'Crosswalk'!$C$2:$C$115)</x:f>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G9" s="62" t="n">
         <x:f>F9+COUNTIF('Beer Review'!$E$2:$E$42,A9)-COUNTIF('Beer Review'!$D$2:$D$42,A9)</x:f>
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H9" s="63" t="n">
         <x:f>G9/SUM($G$5:$G$11)</x:f>
-        <x:v>0.04612850082372323</x:v>
+        <x:v>0.04862236628849271</x:v>
       </x:c>
       <x:c r="I9" s="64" t="n">
         <x:f>G9-F9</x:f>
@@ -5001,15 +5022,15 @@
         <x:v>Witbier, hefeweizen, Belgian blond/dark, tripel</x:v>
       </x:c>
       <x:c r="D10" s="62" t="n">
-        <x:f>COUNTIF('Crosswalk'!$B$2:$B$114,A10)</x:f>
+        <x:f>COUNTIF('Crosswalk'!$B$2:$B$115,A10)</x:f>
         <x:v>14</x:v>
       </x:c>
       <x:c r="E10" s="62" t="n">
-        <x:f>COUNTIFS('Crosswalk'!$B$2:$B$114,A10,'Crosswalk'!$D$2:$D$114,"Yes")</x:f>
+        <x:f>COUNTIFS('Crosswalk'!$B$2:$B$115,A10,'Crosswalk'!$D$2:$D$115,"Yes")</x:f>
         <x:v>14</x:v>
       </x:c>
       <x:c r="F10" s="62" t="n">
-        <x:f>SUMIF('Crosswalk'!$B$2:$B$114,A10,'Crosswalk'!$C$2:$C$114)</x:f>
+        <x:f>SUMIF('Crosswalk'!$B$2:$B$115,A10,'Crosswalk'!$C$2:$C$115)</x:f>
         <x:v>32</x:v>
       </x:c>
       <x:c r="G10" s="62" t="n">
@@ -5018,7 +5039,7 @@
       </x:c>
       <x:c r="H10" s="63" t="n">
         <x:f>G10/SUM($G$5:$G$11)</x:f>
-        <x:v>0.054365733113673806</x:v>
+        <x:v>0.05348460291734198</x:v>
       </x:c>
       <x:c r="I10" s="64" t="n">
         <x:f>G10-F10</x:f>
@@ -5039,15 +5060,15 @@
         <x:v>Saison, Berliner Weisse, gose, lambic, wild/Brett ale</x:v>
       </x:c>
       <x:c r="D11" s="62" t="n">
-        <x:f>COUNTIF('Crosswalk'!$B$2:$B$114,A11)</x:f>
+        <x:f>COUNTIF('Crosswalk'!$B$2:$B$115,A11)</x:f>
         <x:v>15</x:v>
       </x:c>
       <x:c r="E11" s="62" t="n">
-        <x:f>COUNTIFS('Crosswalk'!$B$2:$B$114,A11,'Crosswalk'!$D$2:$D$114,"Yes")</x:f>
+        <x:f>COUNTIFS('Crosswalk'!$B$2:$B$115,A11,'Crosswalk'!$D$2:$D$115,"Yes")</x:f>
         <x:v>15</x:v>
       </x:c>
       <x:c r="F11" s="62" t="n">
-        <x:f>SUMIF('Crosswalk'!$B$2:$B$114,A11,'Crosswalk'!$C$2:$C$114)</x:f>
+        <x:f>SUMIF('Crosswalk'!$B$2:$B$115,A11,'Crosswalk'!$C$2:$C$115)</x:f>
         <x:v>52</x:v>
       </x:c>
       <x:c r="G11" s="62" t="n">
@@ -5056,7 +5077,7 @@
       </x:c>
       <x:c r="H11" s="63" t="n">
         <x:f>G11/SUM($G$5:$G$11)</x:f>
-        <x:v>0.08731466227347612</x:v>
+        <x:v>0.08589951377633712</x:v>
       </x:c>
       <x:c r="I11" s="64" t="n">
         <x:f>G11-F11</x:f>
@@ -5068,7 +5089,7 @@
     </x:row>
     <x:row r="13" ht="34" customHeight="1">
       <x:c r="A13" s="67" t="str">
-        <x:v>Final counts apply the 41 beer-level reviews; the other 566 beers inherit their style default. Legacy style “Gluten-Free” remains recipe-dependent and does not occur in the current export.</x:v>
+        <x:v>Final counts apply the 41 beer-level reviews; the other 576 beers inherit their style default. Legacy style “Gluten-Free” remains recipe-dependent and does not occur in the current export.</x:v>
       </x:c>
       <x:c r="B13" s="67"/>
       <x:c r="C13" s="67"/>
